--- a/Data/OHC_fut_totals_output_0_700.xlsx
+++ b/Data/OHC_fut_totals_output_0_700.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harry\01.HarryGrosvenor\02.Research\05.Local_Repos\202404_01.PlioMIP2_ThetaO\Data\01.thetao\03.Futures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B238EF1-1650-4373-8CB6-F1E8B8043BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3366D5C-76DB-4AF2-8757-1E39AD143EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1156,67 +1156,67 @@
         <v>22</v>
       </c>
       <c r="B2">
-        <v>2.1997171254570781E+17</v>
+        <v>2.412412300405857E+17</v>
       </c>
       <c r="C2">
-        <v>2.49775989979718E+26</v>
+        <v>2.7398794549206781E+26</v>
       </c>
       <c r="D2">
-        <v>1135491409.732136</v>
+        <v>1135742615.1656289</v>
       </c>
       <c r="E2">
-        <v>2.5010091304370001E+26</v>
+        <v>2.743202197226294E+26</v>
       </c>
       <c r="F2">
-        <v>1136968522.67644</v>
+        <v>1137119967.7454751</v>
       </c>
       <c r="G2">
-        <v>2.5036235540869512E+26</v>
+        <v>2.7459682237893031E+26</v>
       </c>
       <c r="H2">
-        <v>1138157049.882823</v>
+        <v>1138266548.934165</v>
       </c>
       <c r="I2">
-        <v>2.5078036313797201E+26</v>
+        <v>2.7505806519371939E+26</v>
       </c>
       <c r="J2">
-        <v>1140057329.3525751</v>
+        <v>1140178505.753119</v>
       </c>
       <c r="K2">
-        <v>2.5008296456274279E+26</v>
+        <v>2.7430085117600551E+26</v>
       </c>
       <c r="L2">
-        <v>1136886928.180723</v>
+        <v>1137039680.6957829</v>
       </c>
       <c r="M2">
-        <v>2.5034921361126819E+26</v>
+        <v>2.7458271956786559E+26</v>
       </c>
       <c r="N2">
-        <v>1138097306.7582419</v>
+        <v>1138208089.5611031</v>
       </c>
       <c r="O2">
-        <v>2.509968104745939E+26</v>
+        <v>2.75278864113435E+26</v>
       </c>
       <c r="P2">
-        <v>1141041307.401921</v>
+        <v>1141093767.7076299</v>
       </c>
       <c r="Q2">
-        <v>2.501123884692596E+26</v>
+        <v>2.7433132035584839E+26</v>
       </c>
       <c r="R2">
-        <v>1137020690.409404</v>
+        <v>1137165982.405643</v>
       </c>
       <c r="S2">
-        <v>2.5046932236038521E+26</v>
+        <v>2.747058876532037E+26</v>
       </c>
       <c r="T2">
-        <v>1138643325.824635</v>
+        <v>1138718649.407434</v>
       </c>
       <c r="U2">
-        <v>2.5162994520552199E+26</v>
+        <v>2.7593094863700111E+26</v>
       </c>
       <c r="V2">
-        <v>1143919562.626653</v>
+        <v>1143796806.9992819</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
@@ -1224,67 +1224,67 @@
         <v>23</v>
       </c>
       <c r="B3">
-        <v>2.1420200775137581E+17</v>
+        <v>2.359043435805791E+17</v>
       </c>
       <c r="C3">
-        <v>2.493373480452842E+26</v>
+        <v>2.7425405419227999E+26</v>
       </c>
       <c r="D3">
-        <v>1164028996.0992801</v>
+        <v>1162564665.108006</v>
       </c>
       <c r="E3">
-        <v>2.4972763616920491E+26</v>
+        <v>2.746527109444971E+26</v>
       </c>
       <c r="F3">
-        <v>1165851052.42834</v>
+        <v>1164254573.5944979</v>
       </c>
       <c r="G3">
-        <v>2.4990163188842101E+26</v>
+        <v>2.748409295095447E+26</v>
       </c>
       <c r="H3">
-        <v>1166663349.7594559</v>
+        <v>1165052433.2786009</v>
       </c>
       <c r="I3">
-        <v>2.501219103498861E+26</v>
+        <v>2.7508485520672359E+26</v>
       </c>
       <c r="J3">
-        <v>1167691717.6248059</v>
+        <v>1166086435.847085</v>
       </c>
       <c r="K3">
-        <v>2.4974144472550699E+26</v>
+        <v>2.746669664602229E+26</v>
       </c>
       <c r="L3">
-        <v>1165915517.539788</v>
+        <v>1164315002.815552</v>
       </c>
       <c r="M3">
-        <v>2.4993852432204301E+26</v>
+        <v>2.7487861414095318E+26</v>
       </c>
       <c r="N3">
-        <v>1166835581.7287509</v>
+        <v>1165212178.668772</v>
       </c>
       <c r="O3">
-        <v>2.5040943498920109E+26</v>
+        <v>2.7538399165489149E+26</v>
       </c>
       <c r="P3">
-        <v>1169034023.6205969</v>
+        <v>1167354477.1371591</v>
       </c>
       <c r="Q3">
-        <v>2.4973089579291681E+26</v>
+        <v>2.74655253662765E+26</v>
       </c>
       <c r="R3">
-        <v>1165866269.9500899</v>
+        <v>1164265352.19327</v>
       </c>
       <c r="S3">
-        <v>2.5000897361337128E+26</v>
+        <v>2.7494829562858921E+26</v>
       </c>
       <c r="T3">
-        <v>1167164473.563463</v>
+        <v>1165507558.934258</v>
       </c>
       <c r="U3">
-        <v>2.5093156065408281E+26</v>
+        <v>2.7591949382589071E+26</v>
       </c>
       <c r="V3">
-        <v>1171471562.233623</v>
+        <v>1169624474.2167859</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -1292,67 +1292,67 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>2.02489328454712E+17</v>
+        <v>2.3890710084718499E+17</v>
       </c>
       <c r="C4">
-        <v>2.3231068995539461E+26</v>
+        <v>2.738481905479131E+26</v>
       </c>
       <c r="D4">
-        <v>1147273743.896841</v>
+        <v>1146253876.8283739</v>
       </c>
       <c r="E4">
-        <v>2.3260636744247631E+26</v>
+        <v>2.7415304453371029E+26</v>
       </c>
       <c r="F4">
-        <v>1148733956.587249</v>
+        <v>1147529912.512187</v>
       </c>
       <c r="G4">
-        <v>2.327782819626644E+26</v>
+        <v>2.743434022307722E+26</v>
       </c>
       <c r="H4">
-        <v>1149582961.922493</v>
+        <v>1148326697.942117</v>
       </c>
       <c r="I4">
-        <v>2.3292784884106061E+26</v>
+        <v>2.7453321108170439E+26</v>
       </c>
       <c r="J4">
-        <v>1150321602.7167389</v>
+        <v>1149121186.051759</v>
       </c>
       <c r="K4">
-        <v>2.3258683220427211E+26</v>
+        <v>2.7413310478278209E+26</v>
       </c>
       <c r="L4">
-        <v>1148637481.190973</v>
+        <v>1147446450.1502161</v>
       </c>
       <c r="M4">
-        <v>2.3277040479777222E+26</v>
+        <v>2.743340354845565E+26</v>
       </c>
       <c r="N4">
-        <v>1149544060.292702</v>
+        <v>1148287491.2957571</v>
       </c>
       <c r="O4">
-        <v>2.3312209969390599E+26</v>
+        <v>2.7473771438147289E+26</v>
       </c>
       <c r="P4">
-        <v>1151280916.74246</v>
+        <v>1149977181.1186421</v>
       </c>
       <c r="Q4">
-        <v>2.3260419272959231E+26</v>
+        <v>2.7415174707628581E+26</v>
       </c>
       <c r="R4">
-        <v>1148723216.6983831</v>
+        <v>1147524481.709084</v>
       </c>
       <c r="S4">
-        <v>2.328464691128617E+26</v>
+        <v>2.7441392190419389E+26</v>
       </c>
       <c r="T4">
-        <v>1149919706.3362241</v>
+        <v>1148621874.0719659</v>
       </c>
       <c r="U4">
-        <v>2.334671920214551E+26</v>
+        <v>2.751047384454882E+26</v>
       </c>
       <c r="V4">
-        <v>1152985166.1969011</v>
+        <v>1151513443.802814</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
@@ -1360,67 +1360,67 @@
         <v>25</v>
       </c>
       <c r="B5">
-        <v>2.130042732145864E+17</v>
+        <v>2.345836991521833E+17</v>
       </c>
       <c r="C5">
-        <v>2.4762324918552281E+26</v>
+        <v>2.7239429464338281E+26</v>
       </c>
       <c r="D5">
-        <v>1162527142.993325</v>
+        <v>1161181683.2450509</v>
       </c>
       <c r="E5">
-        <v>2.48023084153378E+26</v>
+        <v>2.7280221602904671E+26</v>
       </c>
       <c r="F5">
-        <v>1164404264.80793</v>
+        <v>1162920599.406482</v>
       </c>
       <c r="G5">
-        <v>2.4826891943161271E+26</v>
+        <v>2.7306495371801259E+26</v>
       </c>
       <c r="H5">
-        <v>1165558397.889509</v>
+        <v>1164040616.2274089</v>
       </c>
       <c r="I5">
-        <v>2.4860814111605981E+26</v>
+        <v>2.734345915834536E+26</v>
       </c>
       <c r="J5">
-        <v>1167150956.0073709</v>
+        <v>1165616334.6885681</v>
       </c>
       <c r="K5">
-        <v>2.4802300287047809E+26</v>
+        <v>2.7280104171673271E+26</v>
       </c>
       <c r="L5">
-        <v>1164403883.2057271</v>
+        <v>1162915593.4648139</v>
       </c>
       <c r="M5">
-        <v>2.4831938348726509E+26</v>
+        <v>2.7311597600165342E+26</v>
       </c>
       <c r="N5">
-        <v>1165795313.5855701</v>
+        <v>1164258117.630214</v>
       </c>
       <c r="O5">
-        <v>2.489103338141988E+26</v>
+        <v>2.737457249779604E+26</v>
       </c>
       <c r="P5">
-        <v>1168569672.6067071</v>
+        <v>1166942656.149229</v>
       </c>
       <c r="Q5">
-        <v>2.480546090313995E+26</v>
+        <v>2.72833520013964E+26</v>
       </c>
       <c r="R5">
-        <v>1164552265.960892</v>
+        <v>1163054044.2495389</v>
       </c>
       <c r="S5">
-        <v>2.4842302749351249E+26</v>
+        <v>2.732212290101619E+26</v>
       </c>
       <c r="T5">
-        <v>1166281895.4023719</v>
+        <v>1164706797.6062269</v>
       </c>
       <c r="U5">
-        <v>2.495101696623898E+26</v>
+        <v>2.7436303324313569E+26</v>
       </c>
       <c r="V5">
-        <v>1171385746.853193</v>
+        <v>1169574161.524097</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
@@ -1428,67 +1428,67 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>2.1314711635738019E+17</v>
+        <v>2.347344451232615E+17</v>
       </c>
       <c r="C6">
-        <v>2.4756909764302091E+26</v>
+        <v>2.7232889827715619E+26</v>
       </c>
       <c r="D6">
-        <v>1161494004.1127551</v>
+        <v>1160157377.559793</v>
       </c>
       <c r="E6">
-        <v>2.4803915964225691E+26</v>
+        <v>2.7282117590641682E+26</v>
       </c>
       <c r="F6">
-        <v>1163699344.7585461</v>
+        <v>1162254545.82584</v>
       </c>
       <c r="G6">
-        <v>2.4820950039655731E+26</v>
+        <v>2.7300614203864421E+26</v>
       </c>
       <c r="H6">
-        <v>1164498514.633379</v>
+        <v>1163042526.1843691</v>
       </c>
       <c r="I6">
-        <v>2.4840212303181662E+26</v>
+        <v>2.7322176990212E+26</v>
       </c>
       <c r="J6">
-        <v>1165402222.0752211</v>
+        <v>1163961129.6017871</v>
       </c>
       <c r="K6">
-        <v>2.4803501492305191E+26</v>
+        <v>2.7281776884643592E+26</v>
       </c>
       <c r="L6">
-        <v>1163679899.4135849</v>
+        <v>1162240031.2965419</v>
       </c>
       <c r="M6">
-        <v>2.48276502346918E+26</v>
+        <v>2.7307448035235219E+26</v>
       </c>
       <c r="N6">
-        <v>1164812860.6658559</v>
+        <v>1163333656.502598</v>
       </c>
       <c r="O6">
-        <v>2.4871308578695179E+26</v>
+        <v>2.7354644748792729E+26</v>
       </c>
       <c r="P6">
-        <v>1166861133.462105</v>
+        <v>1165344299.3604341</v>
       </c>
       <c r="Q6">
-        <v>2.480479952686504E+26</v>
+        <v>2.7283020665257041E+26</v>
       </c>
       <c r="R6">
-        <v>1163740797.941421</v>
+        <v>1162293018.0072401</v>
       </c>
       <c r="S6">
-        <v>2.483366936948145E+26</v>
+        <v>2.7313529743197301E+26</v>
       </c>
       <c r="T6">
-        <v>1165095254.1081181</v>
+        <v>1163592745.3618779</v>
       </c>
       <c r="U6">
-        <v>2.4922846874799329E+26</v>
+        <v>2.7407604412621931E+26</v>
       </c>
       <c r="V6">
-        <v>1169279101.717314</v>
+        <v>1167600451.575392</v>
       </c>
     </row>
     <row r="7" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1497,87 +1497,87 @@
       </c>
       <c r="B7" s="1">
         <f>AVERAGE(B2:B6)</f>
-        <v>2.1256288766475245E+17</v>
+        <v>2.3707416374875894E+17</v>
       </c>
       <c r="C7" s="1">
         <f>AVERAGE(C2:C6)</f>
-        <v>2.4532327496178812E+26</v>
+        <v>2.7336267663056001E+26</v>
       </c>
       <c r="D7" s="1">
         <f t="shared" ref="D7:V7" si="0">AVERAGE(D2:D6)</f>
-        <v>1154163059.3668675</v>
+        <v>1153180043.5813706</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="0"/>
-        <v>2.4569943209020319E+26</v>
+        <v>2.7374987342726007E+26</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" si="0"/>
-        <v>1155931428.2517009</v>
+        <v>1154815919.8168964</v>
       </c>
       <c r="G7" s="1">
         <f t="shared" si="0"/>
-        <v>2.4590413781759014E+26</v>
+        <v>2.7397044997518085E+26</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" si="0"/>
-        <v>1156892054.8175321</v>
+        <v>1155745764.5133321</v>
       </c>
       <c r="I7" s="1">
         <f t="shared" si="0"/>
-        <v>2.4616807729535901E+26</v>
+        <v>2.7426649859354416E+26</v>
       </c>
       <c r="J7" s="1">
         <f t="shared" si="0"/>
-        <v>1158124765.5553422</v>
+        <v>1156992718.3884635</v>
       </c>
       <c r="K7" s="1">
         <f t="shared" si="0"/>
-        <v>2.4569385185721038E+26</v>
+        <v>2.7374394659643584E+26</v>
       </c>
       <c r="L7" s="1">
         <f t="shared" si="0"/>
-        <v>1155904741.9061589</v>
+        <v>1154791351.6845813</v>
       </c>
       <c r="M7" s="1">
         <f t="shared" si="0"/>
-        <v>2.4593080571305331E+26</v>
+        <v>2.7399716510947618E+26</v>
       </c>
       <c r="N7" s="1">
         <f t="shared" si="0"/>
-        <v>1157017024.6062241</v>
+        <v>1155859906.7316887</v>
       </c>
       <c r="O7" s="1">
         <f t="shared" si="0"/>
-        <v>2.4643035295177034E+26</v>
+        <v>2.745385485231374E+26</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="0"/>
-        <v>1159357410.766758</v>
+        <v>1158142476.2946191</v>
       </c>
       <c r="Q7" s="1">
         <f t="shared" si="0"/>
-        <v>2.457100162583637E+26</v>
+        <v>2.7376040955228677E+26</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="0"/>
-        <v>1155980648.1920381</v>
+        <v>1154860575.7129552</v>
       </c>
       <c r="S7" s="1">
         <f t="shared" si="0"/>
-        <v>2.4601689725498906E+26</v>
+        <v>2.7408492632562431E+26</v>
       </c>
       <c r="T7" s="1">
         <f t="shared" si="0"/>
-        <v>1157420931.0469623</v>
+        <v>1156229525.0763526</v>
       </c>
       <c r="U7" s="1">
         <f t="shared" si="0"/>
-        <v>2.4695346725828863E+26</v>
+        <v>2.7507885165554703E+26</v>
       </c>
       <c r="V7" s="1">
         <f t="shared" si="0"/>
-        <v>1161808227.9255369</v>
+        <v>1160421867.6236739</v>
       </c>
     </row>
   </sheetData>
